--- a/docs/workbook-split/dateien/Prüfungen.xlsx
+++ b/docs/workbook-split/dateien/Prüfungen.xlsx
@@ -691,21 +691,19 @@
           <t>Forecast EBITDA Basis</t>
         </is>
       </c>
-      <c r="D7" s="6">
-        <f>SUM('[Forecast.xlsx]Forecast'!J7:J18)</f>
-        <v/>
-      </c>
-      <c r="E7" s="6">
-        <f>'[D Finanzen.xlsx]D Finanzen'!E39</f>
-        <v/>
-      </c>
-      <c r="F7" s="6">
-        <f>ROUND(D7-E7,2)</f>
-        <v/>
-      </c>
-      <c r="G7" s="1">
-        <f>IF(ABS(F7)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D7" s="6" t="n">
+        <v>439877.29</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>439877.29</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
@@ -728,21 +726,19 @@
           <t>Gesamtleistung YTD</t>
         </is>
       </c>
-      <c r="D8" s="6">
-        <f>'[GuV.xlsx]GuV'!D9</f>
-        <v/>
-      </c>
-      <c r="E8" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$8:$E$16,'[D Finanzen.xlsx]D Finanzen'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$8:$B$16,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="F8" s="6">
-        <f>ROUND(D8-E8,2)</f>
-        <v/>
-      </c>
-      <c r="G8" s="1">
-        <f>IF(ABS(F8)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D8" s="6" t="n">
+        <v>17098817.86</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>17098817.86</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
@@ -765,21 +761,19 @@
           <t>KLR DB4 YTD</t>
         </is>
       </c>
-      <c r="D9" s="6">
-        <f>'[KLR.xlsx]KLR'!M20</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$Q$8:$Q$16,'[D KLR.xlsx]D KLR'!$A$8:$A$16,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$8:$B$16,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="F9" s="6">
-        <f>ROUND(D9-E9,2)</f>
-        <v/>
-      </c>
-      <c r="G9" s="1">
-        <f>IF(ABS(F9)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D9" s="6" t="n">
+        <v>2939188.760000001</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>2939188.760000001</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
@@ -802,21 +796,19 @@
           <t>Bilanz Aktiva / Passiva</t>
         </is>
       </c>
-      <c r="D10" s="6">
-        <f>'[Bilanz.xlsx]Bilanz'!K8</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>'[Bilanz.xlsx]Bilanz'!K10</f>
-        <v/>
-      </c>
-      <c r="F10" s="6">
-        <f>ROUND(D10-E10,2)</f>
-        <v/>
-      </c>
-      <c r="G10" s="1">
-        <f>IF(ABS(F10)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D10" s="6" t="n">
+        <v>6753194.719999998</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>6753194.719999999</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
@@ -839,21 +831,19 @@
           <t>Stunden Monatsdetails</t>
         </is>
       </c>
-      <c r="D11" s="6">
-        <f>'[Stunden.xlsx]Stunden'!I20</f>
-        <v/>
-      </c>
-      <c r="E11" s="6">
-        <f>SUM('[D KLR.xlsx]D KLR'!$G$1142:$G$1146)</f>
-        <v/>
-      </c>
-      <c r="F11" s="6">
-        <f>ROUND(D11-E11,2)</f>
-        <v/>
-      </c>
-      <c r="G11" s="1">
-        <f>IF(ABS(F11)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D11" s="6" t="n">
+        <v>34691.75</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>34691.75</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -876,21 +866,19 @@
           <t>Risiko-Brutto</t>
         </is>
       </c>
-      <c r="D12" s="6">
-        <f>SUM('[Risiken.xlsx]Risiken'!K7:K2271)</f>
-        <v/>
-      </c>
-      <c r="E12" s="6">
-        <f>SUM('[D Risiken.xlsx]D Risiken'!$I$8:$I$2272)</f>
-        <v/>
-      </c>
-      <c r="F12" s="6">
-        <f>ROUND(D12-E12,2)</f>
-        <v/>
-      </c>
-      <c r="G12" s="1">
-        <f>IF(ABS(F12)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D12" s="6" t="n">
+        <v>7686790.620000019</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>7686790.620000019</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
@@ -913,21 +901,19 @@
           <t>KV-Ergebnis gesamt</t>
         </is>
       </c>
-      <c r="D13" s="6">
-        <f>SUM('[Kostenverfolgung.xlsx]Kostenverfolgung'!N7:N294)</f>
-        <v/>
-      </c>
-      <c r="E13" s="6">
-        <f>SUM('[D Projekte.xlsx]D Projekte'!$Q$1127:$Q$1414)</f>
-        <v/>
-      </c>
-      <c r="F13" s="6">
-        <f>ROUND(D13-E13,2)</f>
-        <v/>
-      </c>
-      <c r="G13" s="1">
-        <f>IF(ABS(F13)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D13" s="6" t="n">
+        <v>22592418.28999999</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>22592418.28999999</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
@@ -950,21 +936,19 @@
           <t>Bestandslücke</t>
         </is>
       </c>
-      <c r="D14" s="6">
-        <f>SUM(Bestände!I7:I106)</f>
-        <v/>
-      </c>
-      <c r="E14" s="6">
-        <f>SUM('[D Projekte.xlsx]D Projekte'!$I$400:$I$499)</f>
-        <v/>
-      </c>
-      <c r="F14" s="6">
-        <f>ROUND(D14-E14,2)</f>
-        <v/>
-      </c>
-      <c r="G14" s="1">
-        <f>IF(ABS(F14)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D14" s="6" t="n">
+        <v>-3043579.819999999</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-3043579.82</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
@@ -987,21 +971,19 @@
           <t>Kalkulation Limitpreis</t>
         </is>
       </c>
-      <c r="D15" s="6">
-        <f>'[Kalkulation.xlsx]Kalkulation'!H16</f>
-        <v/>
-      </c>
-      <c r="E15" s="6">
-        <f>163.7974</f>
-        <v/>
-      </c>
-      <c r="F15" s="6">
-        <f>ROUND(D15-E15,2)</f>
-        <v/>
-      </c>
-      <c r="G15" s="1">
-        <f>IF(ABS(F15)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D15" s="6" t="n">
+        <v>163.7974234281201</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>163.7974</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
@@ -1024,21 +1006,19 @@
           <t>Kalkulation Zielpreis</t>
         </is>
       </c>
-      <c r="D16" s="6">
-        <f>'[Kalkulation.xlsx]Kalkulation'!H19</f>
-        <v/>
-      </c>
-      <c r="E16" s="6">
-        <f>178.014</f>
-        <v/>
-      </c>
-      <c r="F16" s="6">
-        <f>ROUND(D16-E16,2)</f>
-        <v/>
-      </c>
-      <c r="G16" s="1">
-        <f>IF(ABS(F16)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D16" s="6" t="n">
+        <v>178.014038116839</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>178.014</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
@@ -1061,21 +1041,19 @@
           <t>Stundensatz ohne VGK</t>
         </is>
       </c>
-      <c r="D17" s="6">
-        <f>Stundensätze!H42</f>
-        <v/>
-      </c>
-      <c r="E17" s="6">
-        <f>34.4781690140845</f>
-        <v/>
-      </c>
-      <c r="F17" s="6">
-        <f>ROUND(D17-E17,2)</f>
-        <v/>
-      </c>
-      <c r="G17" s="1">
-        <f>IF(ABS(F17)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D17" s="6" t="n">
+        <v>34.47816901408451</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>34.4781690140845</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
@@ -1098,21 +1076,19 @@
           <t>Stundensatz mit VGK</t>
         </is>
       </c>
-      <c r="D18" s="6">
-        <f>Stundensätze!H43</f>
-        <v/>
-      </c>
-      <c r="E18" s="6">
-        <f>48.959</f>
-        <v/>
-      </c>
-      <c r="F18" s="6">
-        <f>ROUND(D18-E18,2)</f>
-        <v/>
-      </c>
-      <c r="G18" s="1">
-        <f>IF(ABS(F18)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D18" s="6" t="n">
+        <v>48.959</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>48.959</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
@@ -1135,21 +1111,19 @@
           <t>Umlagen Gesamt</t>
         </is>
       </c>
-      <c r="D19" s="6">
-        <f>SUM('[Umlagen.xlsx]Umlagen'!G7:G25)</f>
-        <v/>
-      </c>
-      <c r="E19" s="6">
-        <f>SUM('[D KLR.xlsx]D KLR'!$E$763:$E$781)</f>
-        <v/>
-      </c>
-      <c r="F19" s="6">
-        <f>ROUND(D19-E19,2)</f>
-        <v/>
-      </c>
-      <c r="G19" s="1">
-        <f>IF(ABS(F19)&lt;=0.02,"OK","Abweichung")</f>
-        <v/>
+      <c r="D19" s="6" t="n">
+        <v>-632002.7199999999</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-632002.72</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
@@ -1308,9 +1282,8 @@
       <c r="G26" s="8" t="n">
         <v>639565.45</v>
       </c>
-      <c r="H26" s="8">
-        <f>G26-F26</f>
-        <v/>
+      <c r="H26" s="8" t="n">
+        <v>639565.45</v>
       </c>
       <c r="I26" s="8" t="n">
         <v>639565.45</v>
@@ -1342,9 +1315,8 @@
       <c r="G27" s="8" t="n">
         <v>1280847.26</v>
       </c>
-      <c r="H27" s="8">
-        <f>G27-F27</f>
-        <v/>
+      <c r="H27" s="8" t="n">
+        <v>1280847.26</v>
       </c>
       <c r="I27" s="8" t="n">
         <v>1280847.26</v>
@@ -1376,9 +1348,8 @@
       <c r="G28" s="8" t="n">
         <v>12030.21</v>
       </c>
-      <c r="H28" s="8">
-        <f>G28-F28</f>
-        <v/>
+      <c r="H28" s="8" t="n">
+        <v>12030.21</v>
       </c>
       <c r="I28" s="8" t="n">
         <v>12030.21</v>
@@ -1410,9 +1381,8 @@
       <c r="G29" s="8" t="n">
         <v>-1080421</v>
       </c>
-      <c r="H29" s="8">
-        <f>G29-F29</f>
-        <v/>
+      <c r="H29" s="8" t="n">
+        <v>-1080421</v>
       </c>
       <c r="I29" s="8" t="n">
         <v>-1080421</v>
@@ -1444,9 +1414,8 @@
       <c r="G30" s="8" t="n">
         <v>-338608.8</v>
       </c>
-      <c r="H30" s="8">
-        <f>G30-F30</f>
-        <v/>
+      <c r="H30" s="8" t="n">
+        <v>-338608.8</v>
       </c>
       <c r="I30" s="8" t="n">
         <v>-314657.29</v>
@@ -1478,9 +1447,8 @@
       <c r="G31" s="8" t="n">
         <v>-9645.450000000001</v>
       </c>
-      <c r="H31" s="8">
-        <f>G31-F31</f>
-        <v/>
+      <c r="H31" s="8" t="n">
+        <v>-9645.450000000001</v>
       </c>
       <c r="I31" s="8" t="n">
         <v>-9645.450000000001</v>
@@ -1512,9 +1480,8 @@
       <c r="G32" s="8" t="n">
         <v>-223180.95</v>
       </c>
-      <c r="H32" s="8">
-        <f>G32-F32</f>
-        <v/>
+      <c r="H32" s="8" t="n">
+        <v>-223180.95</v>
       </c>
       <c r="I32" s="8" t="n">
         <v>-220820.47</v>
@@ -1546,9 +1513,8 @@
       <c r="G33" s="8" t="n">
         <v>-5854.47</v>
       </c>
-      <c r="H33" s="8">
-        <f>G33-F33</f>
-        <v/>
+      <c r="H33" s="8" t="n">
+        <v>-5854.47</v>
       </c>
       <c r="I33" s="8" t="n">
         <v>-5854.47</v>
@@ -1582,9 +1548,8 @@
       <c r="G34" s="8" t="n">
         <v>2777244.65</v>
       </c>
-      <c r="H34" s="8">
-        <f>G34-F34</f>
-        <v/>
+      <c r="H34" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I34" s="8" t="n">
         <v>3416810.1</v>
@@ -1618,9 +1583,8 @@
       <c r="G35" s="8" t="n">
         <v>-200176.92</v>
       </c>
-      <c r="H35" s="8">
-        <f>G35-F35</f>
-        <v/>
+      <c r="H35" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I35" s="8" t="n">
         <v>1080670.34</v>
@@ -1654,9 +1618,8 @@
       <c r="G36" s="8" t="n">
         <v>22190.76</v>
       </c>
-      <c r="H36" s="8">
-        <f>G36-F36</f>
-        <v/>
+      <c r="H36" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I36" s="8" t="n">
         <v>34220.97</v>
@@ -1690,9 +1653,8 @@
       <c r="G37" s="8" t="n">
         <v>-1706242.27</v>
       </c>
-      <c r="H37" s="8">
-        <f>G37-F37</f>
-        <v/>
+      <c r="H37" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I37" s="8" t="n">
         <v>-2786663.27</v>
@@ -1726,9 +1688,8 @@
       <c r="G38" s="8" t="n">
         <v>-363244</v>
       </c>
-      <c r="H38" s="8">
-        <f>G38-F38</f>
-        <v/>
+      <c r="H38" s="8" t="n">
+        <v>-24751.12</v>
       </c>
       <c r="I38" s="8" t="n">
         <v>-653150.17</v>
@@ -1762,9 +1723,8 @@
       <c r="G39" s="8" t="n">
         <v>-9711.51</v>
       </c>
-      <c r="H39" s="8">
-        <f>G39-F39</f>
-        <v/>
+      <c r="H39" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I39" s="8" t="n">
         <v>-19356.96</v>
@@ -1798,9 +1758,8 @@
       <c r="G40" s="8" t="n">
         <v>-214918.93</v>
       </c>
-      <c r="H40" s="8">
-        <f>G40-F40</f>
-        <v/>
+      <c r="H40" s="8" t="n">
+        <v>-2502.899999999994</v>
       </c>
       <c r="I40" s="8" t="n">
         <v>-433236.5</v>
@@ -1834,9 +1793,8 @@
       <c r="G41" s="8" t="n">
         <v>-6903.55</v>
       </c>
-      <c r="H41" s="8">
-        <f>G41-F41</f>
-        <v/>
+      <c r="H41" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I41" s="8" t="n">
         <v>-12758.02</v>
@@ -1870,9 +1828,8 @@
       <c r="G42" s="8" t="n">
         <v>1213541.38</v>
       </c>
-      <c r="H42" s="8">
-        <f>G42-F42</f>
-        <v/>
+      <c r="H42" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I42" s="8" t="n">
         <v>4630351.48</v>
@@ -1906,9 +1863,8 @@
       <c r="G43" s="8" t="n">
         <v>1198671.49</v>
       </c>
-      <c r="H43" s="8">
-        <f>G43-F43</f>
-        <v/>
+      <c r="H43" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I43" s="8" t="n">
         <v>2279341.83</v>
@@ -1942,9 +1898,8 @@
       <c r="G44" s="8" t="n">
         <v>15409.39</v>
       </c>
-      <c r="H44" s="8">
-        <f>G44-F44</f>
-        <v/>
+      <c r="H44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I44" s="8" t="n">
         <v>49630.36</v>
@@ -1978,9 +1933,8 @@
       <c r="G45" s="8" t="n">
         <v>-1746548.03</v>
       </c>
-      <c r="H45" s="8">
-        <f>G45-F45</f>
-        <v/>
+      <c r="H45" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I45" s="8" t="n">
         <v>-4533211.3</v>
@@ -2014,9 +1968,8 @@
       <c r="G46" s="8" t="n">
         <v>-383792.43</v>
       </c>
-      <c r="H46" s="8">
-        <f>G46-F46</f>
-        <v/>
+      <c r="H46" s="8" t="n">
+        <v>-25489.42999999999</v>
       </c>
       <c r="I46" s="8" t="n">
         <v>-1011453.17</v>
@@ -2050,9 +2003,8 @@
       <c r="G47" s="8" t="n">
         <v>-9824.139999999999</v>
       </c>
-      <c r="H47" s="8">
-        <f>G47-F47</f>
-        <v/>
+      <c r="H47" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I47" s="8" t="n">
         <v>-29181.1</v>
@@ -2086,9 +2038,8 @@
       <c r="G48" s="8" t="n">
         <v>-286856.5</v>
       </c>
-      <c r="H48" s="8">
-        <f>G48-F48</f>
-        <v/>
+      <c r="H48" s="8" t="n">
+        <v>-3284.039999999979</v>
       </c>
       <c r="I48" s="8" t="n">
         <v>-716808.96</v>
@@ -2122,9 +2073,8 @@
       <c r="G49" s="8" t="n">
         <v>-9432.18</v>
       </c>
-      <c r="H49" s="8">
-        <f>G49-F49</f>
-        <v/>
+      <c r="H49" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I49" s="8" t="n">
         <v>-22190.2</v>
@@ -2158,9 +2108,8 @@
       <c r="G50" s="8" t="n">
         <v>678343.59</v>
       </c>
-      <c r="H50" s="8">
-        <f>G50-F50</f>
-        <v/>
+      <c r="H50" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I50" s="8" t="n">
         <v>5308695.07</v>
@@ -2194,9 +2143,8 @@
       <c r="G51" s="8" t="n">
         <v>1261219.89</v>
       </c>
-      <c r="H51" s="8">
-        <f>G51-F51</f>
-        <v/>
+      <c r="H51" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I51" s="8" t="n">
         <v>3540561.72</v>
@@ -2230,9 +2178,8 @@
       <c r="G52" s="8" t="n">
         <v>56063.55</v>
       </c>
-      <c r="H52" s="8">
-        <f>G52-F52</f>
-        <v/>
+      <c r="H52" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I52" s="8" t="n">
         <v>105693.91</v>
@@ -2266,9 +2213,8 @@
       <c r="G53" s="8" t="n">
         <v>-1520583.11</v>
       </c>
-      <c r="H53" s="8">
-        <f>G53-F53</f>
-        <v/>
+      <c r="H53" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I53" s="8" t="n">
         <v>-6053794.41</v>
@@ -2302,9 +2248,8 @@
       <c r="G54" s="8" t="n">
         <v>-383705.5</v>
       </c>
-      <c r="H54" s="8">
-        <f>G54-F54</f>
-        <v/>
+      <c r="H54" s="8" t="n">
+        <v>-26554.60999999999</v>
       </c>
       <c r="I54" s="8" t="n">
         <v>-1368604.06</v>
@@ -2338,9 +2283,8 @@
       <c r="G55" s="8" t="n">
         <v>-9599.860000000001</v>
       </c>
-      <c r="H55" s="8">
-        <f>G55-F55</f>
-        <v/>
+      <c r="H55" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I55" s="8" t="n">
         <v>-38780.96</v>
@@ -2374,9 +2318,8 @@
       <c r="G56" s="8" t="n">
         <v>-275785.95</v>
       </c>
-      <c r="H56" s="8">
-        <f>G56-F56</f>
-        <v/>
+      <c r="H56" s="8" t="n">
+        <v>-10957.04000000004</v>
       </c>
       <c r="I56" s="8" t="n">
         <v>-981637.87</v>
@@ -2410,9 +2353,8 @@
       <c r="G57" s="8" t="n">
         <v>-8779.92</v>
       </c>
-      <c r="H57" s="8">
-        <f>G57-F57</f>
-        <v/>
+      <c r="H57" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I57" s="8" t="n">
         <v>-30970.12</v>
@@ -2446,9 +2388,8 @@
       <c r="G58" s="8" t="n">
         <v>1347585.48</v>
       </c>
-      <c r="H58" s="8">
-        <f>G58-F58</f>
-        <v/>
+      <c r="H58" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I58" s="8" t="n">
         <v>6656280.55</v>
@@ -2482,9 +2423,8 @@
       <c r="G59" s="8" t="n">
         <v>-263604.09</v>
       </c>
-      <c r="H59" s="8">
-        <f>G59-F59</f>
-        <v/>
+      <c r="H59" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I59" s="8" t="n">
         <v>3276957.63</v>
@@ -2518,9 +2458,8 @@
       <c r="G60" s="8" t="n">
         <v>24678.87</v>
       </c>
-      <c r="H60" s="8">
-        <f>G60-F60</f>
-        <v/>
+      <c r="H60" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="I60" s="8" t="n">
         <v>130372.78</v>
@@ -2552,9 +2491,8 @@
       <c r="G61" s="10" t="n">
         <v>-582901.1800000001</v>
       </c>
-      <c r="H61" s="10">
-        <f>G61-F61</f>
-        <v/>
+      <c r="H61" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I61" s="10" t="n">
         <v>-6636695.59</v>
@@ -2581,9 +2519,8 @@
       <c r="G62" s="10" t="n">
         <v>-432453.34</v>
       </c>
-      <c r="H62" s="10">
-        <f>G62-F62</f>
-        <v/>
+      <c r="H62" s="10" t="n">
+        <v>-29404.99000000005</v>
       </c>
       <c r="I62" s="10" t="n">
         <v>-1771652.41</v>
@@ -2610,9 +2547,8 @@
       <c r="G63" s="10" t="n">
         <v>-9655.030000000001</v>
       </c>
-      <c r="H63" s="10">
-        <f>G63-F63</f>
-        <v/>
+      <c r="H63" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I63" s="10" t="n">
         <v>-48435.99</v>
@@ -2639,9 +2575,8 @@
       <c r="G64" s="10" t="n">
         <v>-237116.93</v>
       </c>
-      <c r="H64" s="10">
-        <f>G64-F64</f>
-        <v/>
+      <c r="H64" s="10" t="n">
+        <v>-3030.660000000003</v>
       </c>
       <c r="I64" s="10" t="n">
         <v>-1215724.14</v>
@@ -2668,9 +2603,8 @@
       <c r="G65" s="10" t="n">
         <v>-15584.75</v>
       </c>
-      <c r="H65" s="10">
-        <f>G65-F65</f>
-        <v/>
+      <c r="H65" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I65" s="10" t="n">
         <v>-46554.87</v>
@@ -2697,9 +2631,8 @@
       <c r="G66" s="10" t="n">
         <v>2470042.1</v>
       </c>
-      <c r="H66" s="10">
-        <f>G66-F66</f>
-        <v/>
+      <c r="H66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I66" s="10" t="n">
         <v>9126322.65</v>
@@ -2726,9 +2659,8 @@
       <c r="G67" s="10" t="n">
         <v>314645.23</v>
       </c>
-      <c r="H67" s="10">
-        <f>G67-F67</f>
-        <v/>
+      <c r="H67" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I67" s="10" t="n">
         <v>3591602.86</v>
@@ -2755,9 +2687,8 @@
       <c r="G68" s="10" t="n">
         <v>17068.34</v>
       </c>
-      <c r="H68" s="10">
-        <f>G68-F68</f>
-        <v/>
+      <c r="H68" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I68" s="10" t="n">
         <v>147441.12</v>
@@ -2784,9 +2715,8 @@
       <c r="G69" s="10" t="n">
         <v>-2109049.83</v>
       </c>
-      <c r="H69" s="10">
-        <f>G69-F69</f>
-        <v/>
+      <c r="H69" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I69" s="10" t="n">
         <v>-8745745.42</v>
@@ -2813,9 +2743,8 @@
       <c r="G70" s="10" t="n">
         <v>-378900.06</v>
       </c>
-      <c r="H70" s="10">
-        <f>G70-F70</f>
-        <v/>
+      <c r="H70" s="10" t="n">
+        <v>-25043.10999999999</v>
       </c>
       <c r="I70" s="10" t="n">
         <v>-2125509.36</v>
@@ -2842,9 +2771,8 @@
       <c r="G71" s="10" t="n">
         <v>-9047.959999999999</v>
       </c>
-      <c r="H71" s="10">
-        <f>G71-F71</f>
-        <v/>
+      <c r="H71" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I71" s="10" t="n">
         <v>-57483.95</v>
@@ -2871,9 +2799,8 @@
       <c r="G72" s="10" t="n">
         <v>-255251.92</v>
       </c>
-      <c r="H72" s="10">
-        <f>G72-F72</f>
-        <v/>
+      <c r="H72" s="10" t="n">
+        <v>-4769.370000000024</v>
       </c>
       <c r="I72" s="10" t="n">
         <v>-1466206.69</v>
@@ -2900,9 +2827,8 @@
       <c r="G73" s="10" t="n">
         <v>-12828.32</v>
       </c>
-      <c r="H73" s="10">
-        <f>G73-F73</f>
-        <v/>
+      <c r="H73" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I73" s="10" t="n">
         <v>-59383.19</v>
@@ -2929,9 +2855,8 @@
       <c r="G74" s="10" t="n">
         <v>1323928.2</v>
       </c>
-      <c r="H74" s="10">
-        <f>G74-F74</f>
-        <v/>
+      <c r="H74" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I74" s="10" t="n">
         <v>10450250.85</v>
@@ -2958,9 +2883,8 @@
       <c r="G75" s="10" t="n">
         <v>294716.46</v>
       </c>
-      <c r="H75" s="10">
-        <f>G75-F75</f>
-        <v/>
+      <c r="H75" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I75" s="10" t="n">
         <v>3886319.32</v>
@@ -2987,9 +2911,8 @@
       <c r="G76" s="10" t="n">
         <v>15326.23</v>
       </c>
-      <c r="H76" s="10">
-        <f>G76-F76</f>
-        <v/>
+      <c r="H76" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I76" s="10" t="n">
         <v>162767.35</v>
@@ -3016,9 +2939,8 @@
       <c r="G77" s="10" t="n">
         <v>-1512452.36</v>
       </c>
-      <c r="H77" s="10">
-        <f>G77-F77</f>
-        <v/>
+      <c r="H77" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I77" s="10" t="n">
         <v>-10258197.78</v>
@@ -3045,9 +2967,8 @@
       <c r="G78" s="10" t="n">
         <v>-390395</v>
       </c>
-      <c r="H78" s="10">
-        <f>G78-F78</f>
-        <v/>
+      <c r="H78" s="10" t="n">
+        <v>155194.77</v>
       </c>
       <c r="I78" s="10" t="n">
         <v>-2671099.13</v>
@@ -3074,9 +2995,8 @@
       <c r="G79" s="10" t="n">
         <v>-9082.969999999999</v>
       </c>
-      <c r="H79" s="10">
-        <f>G79-F79</f>
-        <v/>
+      <c r="H79" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I79" s="10" t="n">
         <v>-66566.92</v>
@@ -3103,9 +3023,8 @@
       <c r="G80" s="10" t="n">
         <v>-245246.07</v>
       </c>
-      <c r="H80" s="10">
-        <f>G80-F80</f>
-        <v/>
+      <c r="H80" s="10" t="n">
+        <v>26904.48999999999</v>
       </c>
       <c r="I80" s="10" t="n">
         <v>-1738357.25</v>
@@ -3132,9 +3051,8 @@
       <c r="G81" s="10" t="n">
         <v>-8079.09</v>
       </c>
-      <c r="H81" s="10">
-        <f>G81-F81</f>
-        <v/>
+      <c r="H81" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I81" s="10" t="n">
         <v>-67462.28</v>
@@ -3161,9 +3079,8 @@
       <c r="G82" s="10" t="n">
         <v>854339.84</v>
       </c>
-      <c r="H82" s="10">
-        <f>G82-F82</f>
-        <v/>
+      <c r="H82" s="10" t="n">
+        <v>77600</v>
       </c>
       <c r="I82" s="10" t="n">
         <v>11226990.69</v>
@@ -3190,9 +3107,8 @@
       <c r="G83" s="10" t="n">
         <v>1022525.14</v>
       </c>
-      <c r="H83" s="10">
-        <f>G83-F83</f>
-        <v/>
+      <c r="H83" s="10" t="n">
+        <v>42127.01000000001</v>
       </c>
       <c r="I83" s="10" t="n">
         <v>4866717.45</v>
@@ -3219,9 +3135,8 @@
       <c r="G84" s="10" t="n">
         <v>14281.36</v>
       </c>
-      <c r="H84" s="10">
-        <f>G84-F84</f>
-        <v/>
+      <c r="H84" s="10" t="n">
+        <v>804.3299999999999</v>
       </c>
       <c r="I84" s="10" t="n">
         <v>176244.38</v>
@@ -3248,9 +3163,8 @@
       <c r="G85" s="10" t="n">
         <v>-1436882.3</v>
       </c>
-      <c r="H85" s="10">
-        <f>G85-F85</f>
-        <v/>
+      <c r="H85" s="10" t="n">
+        <v>127500</v>
       </c>
       <c r="I85" s="10" t="n">
         <v>-11822580.08</v>
@@ -3277,9 +3191,8 @@
       <c r="G86" s="10" t="n">
         <v>-399129.54</v>
       </c>
-      <c r="H86" s="10">
-        <f>G86-F86</f>
-        <v/>
+      <c r="H86" s="10" t="n">
+        <v>30735.05000000005</v>
       </c>
       <c r="I86" s="10" t="n">
         <v>-3100963.72</v>
@@ -3306,9 +3219,8 @@
       <c r="G87" s="10" t="n">
         <v>-9109.85</v>
       </c>
-      <c r="H87" s="10">
-        <f>G87-F87</f>
-        <v/>
+      <c r="H87" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I87" s="10" t="n">
         <v>-75676.77</v>
@@ -3335,9 +3247,8 @@
       <c r="G88" s="10" t="n">
         <v>-191884.67</v>
       </c>
-      <c r="H88" s="10">
-        <f>G88-F88</f>
-        <v/>
+      <c r="H88" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I88" s="10" t="n">
         <v>-1930241.92</v>
@@ -3364,9 +3275,8 @@
       <c r="G89" s="10" t="n">
         <v>-12425.47</v>
       </c>
-      <c r="H89" s="10">
-        <f>G89-F89</f>
-        <v/>
+      <c r="H89" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="I89" s="10" t="n">
         <v>-79887.75</v>
@@ -3946,6 +3856,8 @@
         </is>
       </c>
     </row>
+    <row r="120"/>
+    <row r="121"/>
     <row r="122">
       <c r="C122" t="inlineStr">
         <is>
